--- a/InputData/land/CSpULApYbP/na-CO2 Sequestered per Unit Land Area per Year by Pol.xlsx
+++ b/InputData/land/CSpULApYbP/na-CO2 Sequestered per Unit Land Area per Year by Pol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCSC\2021年\EI三期\EPS模型\第2轮更新\land\CSpULApYbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\CSpULApYbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C2CEE4-F385-4411-B36E-51E297058544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DFB1CE-8AF0-4739-84B2-83EBB98A4446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23925" yWindow="2070" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,20 @@
     <definedName name="C_to_CO2">'[2]Conversion Factors'!$A$4</definedName>
     <definedName name="grams_per_ton">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -722,7 +735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -733,13 +746,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -807,40 +818,40 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="4" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="4" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="4" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -868,7 +879,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="conversion factors"/>
@@ -881,22 +892,66 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Conversion Factors"/>
+      <sheetName val="About"/>
+      <sheetName val="CO2 Aff &amp; Ref"/>
+      <sheetName val="VFC-PIIiCRfAaREY"/>
+      <sheetName val="Lost Value Aff &amp; Ref"/>
+      <sheetName val="VFC-LVpIIiCAbAaR"/>
+      <sheetName val="One Time Cost Aff &amp; Ref"/>
+      <sheetName val="VFC-OTCpIIiCAbAaR"/>
+      <sheetName val="Ongoing Cost Aff &amp; Ref"/>
+      <sheetName val="VFC-OCpMCAbAaR"/>
+      <sheetName val="CO2 Set Asides"/>
+      <sheetName val="VFC-PACRfFSA"/>
+      <sheetName val="Lost Value Set Asides"/>
+      <sheetName val="VFC-LVpMCAbFSA"/>
+      <sheetName val="CO2 Avoided Deforestation"/>
+      <sheetName val="VFC-PACRfAD"/>
+      <sheetName val="Lost Value Avoided Deforestatio"/>
+      <sheetName val="VFC-LVpMCAbAD"/>
+      <sheetName val="County Data"/>
+      <sheetName val="Forest Mgmt Costs"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="4">
+          <cell r="A4">
+            <v>3.6666666666666665</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -934,9 +989,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -969,26 +1024,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1021,26 +1059,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1248,7 +1269,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1258,42 +1279,34 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B11" s="5">
         <v>2004</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="14" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B13" s="12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B15"/>
-    </row>
-    <row r="16" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B16" s="7"/>
+    </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>2</v>
@@ -1351,33 +1364,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="8">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="6">
         <v>1.4</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="8">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="6">
         <f>(A2*44/12)/1.10231</f>
         <v>4.6568872035392346</v>
       </c>
@@ -1385,8 +1397,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="8">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="6">
         <f>A3/2.47105</f>
         <v>1.8845782981077819</v>
       </c>
@@ -1394,39 +1406,37 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6">
         <f>A4*10^6</f>
         <v>1884578.2981077819</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="11" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -1434,7 +1444,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1449,7 +1459,7 @@
         <v>0.17980917208834496</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1464,7 +1474,7 @@
         <v>0.38238698685829847</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1479,7 +1489,7 @@
         <v>0.23823759277775738</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1494,7 +1504,7 @@
         <v>0.10379311719603398</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1509,11 +1519,11 @@
         <v>6.7183869842159641E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="41">
         <f>SUMPRODUCT(B11:B15,E11:E15)</f>
         <v>0.52169592688533073</v>
       </c>
@@ -1547,38 +1557,37 @@
         <f>B18*10^6</f>
         <v>702269.15858522756</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A24" s="7">
+      <c r="A24">
         <v>44</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A25" s="7">
+      <c r="A25">
         <v>12</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="12">
+      <c r="A26" s="10">
         <f>A24/A25</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1614,14 +1623,14 @@
   <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="16" customWidth="1"/>
-    <col min="2" max="7" width="14" style="16" customWidth="1"/>
-    <col min="8" max="10" width="9" style="15"/>
-    <col min="11" max="11" width="10.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="10.375" style="14" customWidth="1"/>
+    <col min="2" max="7" width="14" style="14" customWidth="1"/>
+    <col min="8" max="10" width="9" style="13"/>
+    <col min="11" max="11" width="10.25" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="41" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" s="37" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="42" t="s">
         <v>93</v>
       </c>
@@ -1633,963 +1642,963 @@
       <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="39"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="34"/>
+      <c r="E3" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="33" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="35"/>
-      <c r="B4" s="33" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="31" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="26">
         <v>32591.119999999999</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <v>22044.62</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="25">
         <v>8003.1</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="25">
         <v>22.96</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="25">
         <v>1900713.2</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="25">
         <v>1756022.99</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="23">
         <v>107.1</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="22">
         <v>71.819999999999993</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="22">
         <v>43.48</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <v>43.77</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <v>3000.81</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <v>2437.36</v>
       </c>
       <c r="I8" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="38">
         <f>G14+G15+G16</f>
         <v>315749.04000000004</v>
       </c>
-      <c r="L8" s="45">
+      <c r="L8" s="40">
         <f>K8/G6</f>
         <v>0.17980917208834496</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="23">
         <v>20.39</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <v>13.64</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="22">
         <v>12.98</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <v>12.07</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <v>620.55999999999995</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <v>460.27</v>
       </c>
       <c r="I9" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="38">
         <f>G33+G34+G35+G36+G37</f>
         <v>671480.34</v>
       </c>
-      <c r="L9" s="45">
+      <c r="L9" s="40">
         <f>K9/G6</f>
         <v>0.38238698685829847</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="23">
         <v>775.64</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <v>502.69</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="22">
         <v>263.54000000000002</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <v>26.78</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <v>15920.34</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <v>13737.98</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="38">
         <f>SUM(G18:G24)+SUM(G26:G31)</f>
         <v>418350.68999999994</v>
       </c>
-      <c r="L10" s="45">
+      <c r="L10" s="40">
         <f>K10/G6</f>
         <v>0.23823759277775738</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="23">
         <v>787.25</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="22">
         <v>321.08999999999997</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="22">
         <v>167.63</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <v>20.5</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <v>14778.65</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <v>12923.37</v>
       </c>
       <c r="I11" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="39">
         <f>G8+G9+G10+G11+G12</f>
         <v>182263.1</v>
       </c>
-      <c r="L11" s="45">
+      <c r="L11" s="40">
         <f>K11/G6</f>
         <v>0.10379311719603398</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="23">
         <v>4499.17</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="22">
         <v>2614.85</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="22">
         <v>600.01</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <v>22.1</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <v>166271.98000000001</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <v>152704.12</v>
       </c>
       <c r="I12" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="38">
         <f>G40+G41+G42+G43+G39</f>
         <v>117976.42</v>
       </c>
-      <c r="L12" s="45">
+      <c r="L12" s="40">
         <f>K12/G6</f>
         <v>6.7183869842159641E-2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="23">
         <v>735.92</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="22">
         <v>571.83000000000004</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="22">
         <v>315.32</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <v>39.24</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <v>30888.53</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <v>29749.18</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="23">
         <v>904.79</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="22">
         <v>784.87</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="22">
         <v>175.94</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <v>41.49</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <v>105368.45</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <v>101295.77</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="23">
         <v>2453.77</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <v>1990.46</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="22">
         <v>243.26</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <v>43.78</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <v>199999.41</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <v>184704.09</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="23">
         <v>10.19</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <v>8.9</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="22">
         <v>8.9</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="22">
         <v>14.04</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="22">
         <v>664.32</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="22">
         <v>449.59</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="23">
         <v>174.98</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="22">
         <v>155.99</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="22">
         <v>150.83000000000001</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="22">
         <v>15.2</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <v>9609.6200000000008</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="22">
         <v>7044.48</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="23">
         <v>659.77</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <v>604.99</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="22">
         <v>244.65</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="22">
         <v>59.43</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="22">
         <v>31384.86</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="22">
         <v>28114.67</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="23">
         <v>449.33</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <v>395.85</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="22">
         <v>232.91</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="22">
         <v>28.65</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="22">
         <v>26145.1</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="22">
         <v>22186.55</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="23">
         <v>924.4</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="22">
         <v>811.58</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="22">
         <v>385.59</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="22">
         <v>66.8</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="22">
         <v>79711.289999999994</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="22">
         <v>72937.63</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="23">
         <v>1079.9000000000001</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="22">
         <v>1021.02</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="22">
         <v>368.7</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="22">
         <v>61.16</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="22">
         <v>57564.29</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="22">
         <v>50665.83</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="23">
         <v>349.34</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <v>266.51</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="22">
         <v>256.11</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="22">
         <v>17.510000000000002</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="22">
         <v>13040.49</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="22">
         <v>9161.49</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="23">
         <v>520.74</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <v>403.18</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="22">
         <v>245.78</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="22">
         <v>24.14</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="22">
         <v>26564.48</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="22">
         <v>20719.12</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="23">
         <v>876.09</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="22">
         <v>736.27</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="22">
         <v>197.42</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="22">
         <v>39.61</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="22">
         <v>39579.82</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="22">
         <v>36507.910000000003</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="23">
         <v>1257.5899999999999</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="22">
         <v>1052.58</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="22">
         <v>501.51</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="22">
         <v>49.69</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="22">
         <v>46141.03</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="22">
         <v>40715.730000000003</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="23">
         <v>1080.29</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="22">
         <v>945.98</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="22">
         <v>615.51</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="22">
         <v>53.52</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="22">
         <v>50063.49</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="22">
         <v>46755.09</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="23">
         <v>1629.5</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="22">
         <v>1429.65</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="22">
         <v>733.53</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="22">
         <v>60.17</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="22">
         <v>74433.240000000005</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="22">
         <v>67752.45</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="23">
         <v>217.5</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="22">
         <v>194.49</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="22">
         <v>140.4</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="22">
         <v>57.36</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="22">
         <v>16347.14</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="22">
         <v>15340.15</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="23">
         <v>421.71</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="22">
         <v>354.97</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="22">
         <v>95.93</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="22">
         <v>43.11</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="22">
         <v>24412.17</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="22">
         <v>20678.18</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="23">
         <v>2454.52</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="22">
         <v>1839.77</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="22">
         <v>502.22</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="22">
         <v>38.03</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="22">
         <v>197201.77</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="22">
         <v>186099</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="23">
         <v>927.96</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="22">
         <v>771.03</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="22">
         <v>315.45</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="22">
         <v>43.77</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="22">
         <v>44464.57</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="22">
         <v>39182.9</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="23">
         <v>2599.44</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="22">
         <v>2106.16</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="22">
         <v>507.68</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="22">
         <v>55.04</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="22">
         <v>213244.99</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="22">
         <v>197265.84</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="23">
         <v>1798.19</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="22">
         <v>1490.99</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="22">
         <v>7.84</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="22">
         <v>12.14</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="22">
         <v>230519.15</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="22">
         <v>228254.42</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
     </row>
     <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="23">
         <v>1236.79</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="22">
         <v>886.84</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="22">
         <v>310.52999999999997</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="22">
         <v>43.06</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="22">
         <v>51023.42</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="22">
         <v>47866.7</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="23">
         <v>1046.3499999999999</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="22">
         <v>509.73</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="22">
         <v>126.56</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="22">
         <v>11.33</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="22">
         <v>28386.880000000001</v>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="22">
         <v>25188.89</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="23">
         <v>819.16</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="22">
         <v>419.75</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="22">
         <v>19.100000000000001</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="22">
         <v>5.82</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="22">
         <v>5556.86</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="22">
         <v>4864.1499999999996</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="23">
         <v>179.52</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="22">
         <v>65.599999999999994</v>
       </c>
-      <c r="D42" s="24">
+      <c r="D42" s="22">
         <v>43.55</v>
       </c>
-      <c r="E42" s="24">
+      <c r="E42" s="22">
         <v>12.63</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="22">
         <v>1111.1400000000001</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="22">
         <v>835.18</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="23">
         <v>1371.26</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="22">
         <v>802.23</v>
       </c>
-      <c r="D43" s="24">
+      <c r="D43" s="22">
         <v>121.42</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="22">
         <v>4.87</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="22">
         <v>46490.95</v>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="22">
         <v>39221.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="17"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2650,8 +2659,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <f>Calculations!A6</f>
-        <v>1884578.2981077819</v>
+        <v>91741.808767074341</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2701,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>5617478</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -2743,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>4936277</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2785,7 +2793,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>194930.20678155916</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -2829,24 +2837,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3080,25 +3070,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADDB5C7-ECC4-4C51-99FE-CBD4F31EF89A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2887E70D-36D4-4813-B132-0547119682E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A54D4F-A403-4885-89C5-492780163B87}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3116,4 +3106,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADDB5C7-ECC4-4C51-99FE-CBD4F31EF89A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2887E70D-36D4-4813-B132-0547119682E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/land/CSpULApYbP/na-CO2 Sequestered per Unit Land Area per Year by Pol.xlsx
+++ b/InputData/land/CSpULApYbP/na-CO2 Sequestered per Unit Land Area per Year by Pol.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\CSpULApYbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Land\CSpULApYbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DFB1CE-8AF0-4739-84B2-83EBB98A4446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC6AB99-C3D9-4ECE-A72B-B31E8B3AE152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23925" yWindow="2070" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="acres_per_hectare">#REF!</definedName>
@@ -948,6 +949,39 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="About"/>
+      <sheetName val="Calculations"/>
+      <sheetName val="na-CO2 Abated per Unit Land Are"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="J9">
+            <v>250883.0340962171</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="J15">
+            <v>81612.28743035956</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -2659,7 +2693,8 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>91741.808767074341</v>
+        <f>[3]Sheet1!$J$15</f>
+        <v>81612.28743035956</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2793,7 +2828,8 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>194930.20678155916</v>
+        <f>[3]Sheet1!$J$9</f>
+        <v>250883.0340962171</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -2837,6 +2873,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3070,7 +3115,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3079,16 +3124,17 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2887E70D-36D4-4813-B132-0547119682E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A54D4F-A403-4885-89C5-492780163B87}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3108,20 +3154,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADDB5C7-ECC4-4C51-99FE-CBD4F31EF89A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2887E70D-36D4-4813-B132-0547119682E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>